--- a/data/trans_camb/IP1002-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP1002-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,35; 3,41</t>
+          <t>-3,99; 3,83</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,33; 1,22</t>
+          <t>-4,88; 1,3</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,54; 0,49</t>
+          <t>-5,44; 0,69</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,76; 3,8</t>
+          <t>-5,51; 3,53</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,8; 1,15</t>
+          <t>-7,03; 0,48</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-6,7; 1,96</t>
+          <t>-6,84; 1,44</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 2,32</t>
+          <t>-3,34; 2,63</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-5,04; -0,13</t>
+          <t>-5,05; -0,02</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-4,82; 0,38</t>
+          <t>-4,88; 0,32</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>-87,85; 644,02</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>-87,18; 211,65</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-84,59; 248,18</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-79,68; 122,91</t>
+          <t>-70,93; 177,87</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 37,45</t>
+          <t>-100,0; 47,79</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 86,88</t>
+          <t>-100,0; 54,43</t>
         </is>
       </c>
     </row>
@@ -893,37 +893,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 1,52</t>
+          <t>-1,14; 1,47</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 1,04</t>
+          <t>-1,35; 1,09</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 1,19</t>
+          <t>-1,3; 1,21</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,93</t>
+          <t>0,33; 3,12</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 1,68</t>
+          <t>-0,69; 1,52</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 1,92</t>
+          <t>-0,68; 1,91</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,01; 1,91</t>
+          <t>-0,03; 1,9</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 1,11</t>
+          <t>-0,63; 1,1</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-62,02; 191,74</t>
+          <t>-57,38; 216,67</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-72,49; 138,97</t>
+          <t>-67,34; 191,29</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-67,1; 179,28</t>
+          <t>-68,76; 172,09</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,21; 627,19</t>
+          <t>8,51; 711,63</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-50,35; 410,75</t>
+          <t>-52,68; 323,48</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-60,31; 465,15</t>
+          <t>-60,05; 443,11</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-4,25; 261,8</t>
+          <t>-8,56; 230,4</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-48,48; 133,31</t>
+          <t>-46,68; 125,02</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-47,64; 152,17</t>
+          <t>-44,07; 144,16</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 1,23</t>
+          <t>-1,58; 1,42</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 1,58</t>
+          <t>-1,38; 1,71</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 2,83</t>
+          <t>-0,88; 3,09</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 3,58</t>
+          <t>-0,52; 3,57</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 2,51</t>
+          <t>-0,81; 2,75</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 3,72</t>
+          <t>-0,64; 3,29</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 2,09</t>
+          <t>-0,62; 1,96</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 1,68</t>
+          <t>-0,64; 1,76</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 2,5</t>
+          <t>-0,3; 2,44</t>
         </is>
       </c>
     </row>
@@ -1245,17 +1245,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-65,05; —</t>
+          <t>-69,83; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-71,28; 722,98</t>
+          <t>-75,9; 751,6</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-60,1; —</t>
+          <t>-64,32; —</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 1,26</t>
+          <t>-1,0; 1,14</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 0,67</t>
+          <t>-1,23; 0,64</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 1,0</t>
+          <t>-1,11; 0,89</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,08; 2,45</t>
+          <t>0,15; 2,42</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 1,17</t>
+          <t>-0,73; 1,12</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 1,38</t>
+          <t>-0,84; 1,4</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 1,47</t>
+          <t>-0,06; 1,37</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 0,65</t>
+          <t>-0,77; 0,66</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 0,85</t>
+          <t>-0,63; 0,82</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-47,55; 143,43</t>
+          <t>-50,81; 117,38</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-64,08; 89,53</t>
+          <t>-65,32; 77,94</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-60,03; 112,85</t>
+          <t>-59,05; 93,11</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 355,95</t>
+          <t>1,81; 323,08</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-46,97; 166,37</t>
+          <t>-47,64; 151,26</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-52,04; 183,1</t>
+          <t>-53,64; 175,58</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 165,63</t>
+          <t>-6,92; 136,18</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-42,51; 75,95</t>
+          <t>-45,09; 72,62</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-40,87; 91,49</t>
+          <t>-41,31; 89,5</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1002-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP1002-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 3,83</t>
+          <t>-4,15; 3,29</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,88; 1,3</t>
+          <t>-4,94; 1,42</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,44; 0,69</t>
+          <t>-4,9; 0,83</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,51; 3,53</t>
+          <t>-5,42; 3,78</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-7,03; 0,48</t>
+          <t>-6,85; 0,71</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-6,84; 1,44</t>
+          <t>-7,04; 1,99</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 2,63</t>
+          <t>-3,38; 2,47</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-5,05; -0,02</t>
+          <t>-4,52; 0,32</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-4,88; 0,32</t>
+          <t>-4,81; 0,19</t>
         </is>
       </c>
     </row>
@@ -783,7 +783,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-87,85; 644,02</t>
+          <t>-92,42; 332,15</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-87,18; 211,65</t>
+          <t>-86,39; 305,2</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-70,93; 177,87</t>
+          <t>-71,25; 153,56</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 47,79</t>
+          <t>-100,0; 57,49</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 54,43</t>
+          <t>-100,0; 123,48</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 1,47</t>
+          <t>-1,11; 1,51</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 1,09</t>
+          <t>-1,53; 0,96</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 1,21</t>
+          <t>-1,37; 1,27</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,33; 3,12</t>
+          <t>0,18; 2,85</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 1,52</t>
+          <t>-0,67; 1,48</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 1,91</t>
+          <t>-0,76; 1,67</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 1,9</t>
+          <t>-0,01; 1,94</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 0,94</t>
+          <t>-0,64; 0,97</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 1,1</t>
+          <t>-0,62; 1,16</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-57,38; 216,67</t>
+          <t>-57,6; 192,69</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-67,34; 191,29</t>
+          <t>-74,49; 134,05</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-68,76; 172,09</t>
+          <t>-67,89; 189,97</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8,51; 711,63</t>
+          <t>-0,75; 598,46</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-52,68; 323,48</t>
+          <t>-50,66; 321,36</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-60,05; 443,11</t>
+          <t>-63,57; 337,86</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-8,56; 230,4</t>
+          <t>-3,96; 261,92</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-46,68; 125,02</t>
+          <t>-46,29; 143,91</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-44,07; 144,16</t>
+          <t>-44,73; 157,22</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 1,42</t>
+          <t>-1,61; 1,47</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 1,71</t>
+          <t>-1,31; 1,61</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 3,09</t>
+          <t>-0,89; 2,87</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 3,57</t>
+          <t>-0,51; 3,66</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 2,75</t>
+          <t>-0,87; 2,43</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 3,29</t>
+          <t>-0,57; 3,61</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 1,96</t>
+          <t>-0,54; 1,95</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 1,76</t>
+          <t>-0,62; 1,8</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 2,44</t>
+          <t>-0,29; 2,46</t>
         </is>
       </c>
     </row>
@@ -1245,17 +1245,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-69,83; —</t>
+          <t>-69,51; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-75,9; 751,6</t>
+          <t>-70,87; 805,02</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-64,32; —</t>
+          <t>-72,14; 1263,17</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 1,14</t>
+          <t>-0,81; 1,22</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 0,64</t>
+          <t>-1,22; 0,68</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 0,89</t>
+          <t>-1,1; 1,04</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,15; 2,42</t>
+          <t>0,15; 2,39</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 1,12</t>
+          <t>-0,76; 1,13</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 1,4</t>
+          <t>-0,77; 1,43</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 1,37</t>
+          <t>-0,06; 1,47</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 0,66</t>
+          <t>-0,8; 0,61</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 0,82</t>
+          <t>-0,65; 0,82</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-50,81; 117,38</t>
+          <t>-44,54; 139,71</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-65,32; 77,94</t>
+          <t>-64,16; 73,01</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-59,05; 93,11</t>
+          <t>-56,64; 127,22</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,81; 323,08</t>
+          <t>1,73; 336,25</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-47,64; 151,26</t>
+          <t>-47,18; 160,47</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-53,64; 175,58</t>
+          <t>-52,82; 163,65</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-6,92; 136,18</t>
+          <t>-6,37; 157,09</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-45,09; 72,62</t>
+          <t>-46,57; 68,96</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-41,31; 89,5</t>
+          <t>-42,55; 82,58</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1002-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP1002-Estudios-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-0,76</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-2,89</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-2,31</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-0,1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-1,79</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-2,03</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-0,76</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-2,89</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-2,5</t>
+          <t>-2,01</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-2,23</t>
+          <t>-2,11</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,15; 3,29</t>
+          <t>-4,76; 3,8</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,94; 1,42</t>
+          <t>-6,8; 1,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,9; 0,83</t>
+          <t>-6,29; 3,18</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,42; 3,78</t>
+          <t>-4,35; 3,41</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,85; 0,71</t>
+          <t>-5,33; 1,22</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-7,04; 1,99</t>
+          <t>-5,53; 0,7</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 2,47</t>
+          <t>-3,64; 2,32</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-4,52; 0,32</t>
+          <t>-5,04; -0,13</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-4,81; 0,19</t>
+          <t>-4,73; 0,72</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-19,46%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-74,25%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-59,35%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>-3,67%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-65,35%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-73,92%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-19,46%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-74,25%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-64,23%</t>
+          <t>-73,46%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-67,47%</t>
+          <t>-63,8%</t>
         </is>
       </c>
     </row>
@@ -783,7 +783,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-92,42; 332,15</t>
+          <t>-84,59; 248,18</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-86,39; 305,2</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-71,25; 153,56</t>
+          <t>-79,68; 122,91</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 57,49</t>
+          <t>-100,0; 37,45</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 123,48</t>
+          <t>-100,0; 129,2</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1,57</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,48</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0,4</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>0,2</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-0,22</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-0,1</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1,57</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,48</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,44</t>
+          <t>0,01</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,19</t>
+          <t>0,22</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 1,51</t>
+          <t>0,32; 2,93</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 0,96</t>
+          <t>-0,55; 1,68</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 1,27</t>
+          <t>-0,6; 1,99</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,18; 2,85</t>
+          <t>-1,16; 1,52</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 1,48</t>
+          <t>-1,48; 1,04</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 1,67</t>
+          <t>-1,3; 1,38</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 1,94</t>
+          <t>0,01; 1,91</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 0,97</t>
+          <t>-0,69; 0,94</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 1,16</t>
+          <t>-0,68; 1,13</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>172,89%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>52,84%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>44,03%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>14,23%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-16,1%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-6,99%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>172,89%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>52,84%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>48,28%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>19,32%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-57,6; 192,69</t>
+          <t>0,21; 627,19</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-74,49; 134,05</t>
+          <t>-50,35; 410,75</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-67,89; 189,97</t>
+          <t>-61,56; 473,26</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 598,46</t>
+          <t>-62,02; 191,74</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-50,66; 321,36</t>
+          <t>-72,49; 138,97</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-63,57; 337,86</t>
+          <t>-65,56; 192,36</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-3,96; 261,92</t>
+          <t>-4,25; 261,8</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-46,29; 143,91</t>
+          <t>-48,48; 133,31</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-44,73; 157,22</t>
+          <t>-47,25; 149,84</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>1,28</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0,88</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1,13</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>-0,02</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>0,2</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,83</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1,28</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0,88</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,04</t>
+          <t>0,75</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,93</t>
+          <t>0,94</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 1,47</t>
+          <t>-0,52; 3,58</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 1,61</t>
+          <t>-0,66; 2,51</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 2,87</t>
+          <t>-0,51; 3,98</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 3,66</t>
+          <t>-1,58; 1,23</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 2,43</t>
+          <t>-1,49; 1,58</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 3,61</t>
+          <t>-0,94; 2,79</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 1,95</t>
+          <t>-0,48; 2,09</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 1,8</t>
+          <t>-0,64; 1,68</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 2,46</t>
+          <t>-0,35; 2,54</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>248,18%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>170,58%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>220,0%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>-2,12%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>25,99%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>108,69%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>248,18%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>170,58%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>202,55%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>143,8%</t>
+          <t>145,55%</t>
         </is>
       </c>
     </row>
@@ -1245,17 +1245,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-69,51; —</t>
+          <t>-65,05; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-70,87; 805,02</t>
+          <t>-71,28; 722,98</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-72,14; 1263,17</t>
+          <t>-61,7; inf</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>1,21</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0,17</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0,23</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>0,12</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-0,31</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-0,1</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1,21</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>0,17</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,22</t>
+          <t>-0,03</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,07</t>
+          <t>0,1</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 1,22</t>
+          <t>0,08; 2,45</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 0,68</t>
+          <t>-0,72; 1,17</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 1,04</t>
+          <t>-0,83; 1,38</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,15; 2,39</t>
+          <t>-0,87; 1,26</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 1,13</t>
+          <t>-1,21; 0,67</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 1,43</t>
+          <t>-1,07; 1,08</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 1,47</t>
+          <t>-0,02; 1,47</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 0,61</t>
+          <t>-0,69; 0,65</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 0,82</t>
+          <t>-0,66; 0,89</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>102,75%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>14,63%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>19,56%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>8,33%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-22,18%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-6,91%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>102,75%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>14,63%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>-2,42%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>7,96%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-44,54; 139,71</t>
+          <t>-3,8; 355,95</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-64,16; 73,01</t>
+          <t>-46,97; 166,37</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-56,64; 127,22</t>
+          <t>-51,92; 183,8</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,73; 336,25</t>
+          <t>-47,55; 143,43</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-47,18; 160,47</t>
+          <t>-64,08; 89,53</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-52,82; 163,65</t>
+          <t>-58,92; 120,8</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-6,37; 157,09</t>
+          <t>-1,46; 165,63</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-46,57; 68,96</t>
+          <t>-42,51; 75,95</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-42,55; 82,58</t>
+          <t>-40,54; 95,09</t>
         </is>
       </c>
     </row>
